--- a/data/trans_bre/P2C_R2-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R2-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 16,57</t>
+          <t>-0,87; 17,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,41; 19,91</t>
+          <t>2,08; 19,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 11,38</t>
+          <t>-4,44; 12,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 6,09</t>
+          <t>-0,94; 6,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 53,96</t>
+          <t>-2,27; 55,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,86; 49,76</t>
+          <t>4,1; 45,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-13,31; 33,62</t>
+          <t>-10,68; 36,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-13,63; 150,5</t>
+          <t>-13,29; 147,03</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,24; 13,39</t>
+          <t>2,08; 12,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 11,52</t>
+          <t>-0,76; 12,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,83; 13,22</t>
+          <t>1,37; 13,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,85; 13,26</t>
+          <t>4,39; 13,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,84; 65,62</t>
+          <t>7,51; 63,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 28,22</t>
+          <t>-1,64; 29,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,53; 54,95</t>
+          <t>4,8; 54,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>28,12; 159,64</t>
+          <t>34,29; 161,57</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 8,53</t>
+          <t>-5,53; 9,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 14,34</t>
+          <t>-1,73; 13,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 10,82</t>
+          <t>-2,56; 11,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 5,74</t>
+          <t>-3,59; 5,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-17,18; 28,66</t>
+          <t>-14,97; 31,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 34,93</t>
+          <t>-3,5; 33,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 47,27</t>
+          <t>-9,26; 48,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-23,56; 61,28</t>
+          <t>-23,46; 63,09</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,8; 15,53</t>
+          <t>2,26; 15,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 13,39</t>
+          <t>-1,58; 13,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,6; 17,17</t>
+          <t>2,64; 16,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 3,66</t>
+          <t>-10,47; 3,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,37; 59,93</t>
+          <t>7,81; 60,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 28,49</t>
+          <t>-2,86; 29,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,78; 66,0</t>
+          <t>7,76; 64,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-53,47; 28,81</t>
+          <t>-52,42; 28,69</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 15,89</t>
+          <t>-0,69; 16,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 18,83</t>
+          <t>-1,31; 18,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 14,1</t>
+          <t>-4,92; 13,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 3,34</t>
+          <t>-8,1; 3,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 77,59</t>
+          <t>-2,63; 85,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 44,63</t>
+          <t>-2,25; 44,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,54; 38,81</t>
+          <t>-10,55; 36,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-58,63; 36,57</t>
+          <t>-56,26; 41,19</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,36; 2,75</t>
+          <t>-13,74; 1,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 15,27</t>
+          <t>-3,15; 14,63</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 11,95</t>
+          <t>-3,84; 12,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,18; 12,07</t>
+          <t>0,21; 12,21</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-34,36; 8,51</t>
+          <t>-35,8; 7,1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 38,56</t>
+          <t>-6,38; 35,79</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-13,74; 48,38</t>
+          <t>-11,99; 49,96</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,64; 80,02</t>
+          <t>0,21; 79,81</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,04; 15,61</t>
+          <t>5,03; 15,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 9,62</t>
+          <t>-1,16; 10,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,11; 15,29</t>
+          <t>4,67; 14,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,11; 55,2</t>
+          <t>1,19; 59,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>15,07; 58,19</t>
+          <t>16,14; 60,08</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 23,17</t>
+          <t>-2,54; 24,33</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,52; 64,17</t>
+          <t>15,96; 62,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>18,07; 1846,02</t>
+          <t>19,63; 1408,93</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 6,81</t>
+          <t>-2,1; 6,76</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,44; 14,07</t>
+          <t>4,07; 13,74</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,5; 14,34</t>
+          <t>4,62; 14,17</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,41; 24,0</t>
+          <t>6,82; 25,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 25,8</t>
+          <t>-6,59; 25,86</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,62; 36,33</t>
+          <t>9,14; 35,77</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,98; 43,66</t>
+          <t>12,25; 43,11</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>31,86; 337,82</t>
+          <t>29,66; 313,13</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,03; 7,64</t>
+          <t>3,11; 7,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,63; 9,63</t>
+          <t>4,44; 9,13</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,06; 9,87</t>
+          <t>5,2; 9,97</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,97; 24,36</t>
+          <t>4,08; 24,31</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,83; 27,14</t>
+          <t>10,26; 27,4</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,2; 22,37</t>
+          <t>9,73; 21,1</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,69; 33,01</t>
+          <t>15,81; 32,61</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>30,74; 208,36</t>
+          <t>31,86; 234,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2C_R2-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R2-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,7</t>
+          <t>3,25</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>55,96%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 17,31</t>
+          <t>-1,04; 16,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,08; 19,17</t>
+          <t>2,44; 19,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 12,05</t>
+          <t>-5,86; 11,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 6,02</t>
+          <t>-0,25; 6,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 55,41</t>
+          <t>-2,44; 56,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,1; 45,27</t>
+          <t>4,91; 47,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 36,63</t>
+          <t>-13,45; 32,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-13,29; 147,03</t>
+          <t>-5,89; 151,37</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,9</t>
+          <t>8,84</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>75,0%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,08; 12,96</t>
+          <t>1,77; 13,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 12,11</t>
+          <t>-0,8; 12,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,37; 13,09</t>
+          <t>1,72; 12,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,39; 13,09</t>
+          <t>4,13; 13,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,51; 63,83</t>
+          <t>6,9; 65,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 29,03</t>
+          <t>-1,69; 30,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,8; 54,96</t>
+          <t>6,05; 53,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,29; 161,57</t>
+          <t>28,65; 143,96</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,23</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 9,34</t>
+          <t>-5,85; 8,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 13,73</t>
+          <t>-1,78; 14,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 11,22</t>
+          <t>-3,17; 10,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 5,72</t>
+          <t>-4,26; 4,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,97; 31,97</t>
+          <t>-15,37; 27,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 33,63</t>
+          <t>-4,11; 34,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 48,07</t>
+          <t>-11,34; 43,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-23,46; 63,09</t>
+          <t>-28,7; 50,17</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,37</t>
+          <t>0,67</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-15,21%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,26; 15,35</t>
+          <t>2,02; 16,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 13,5</t>
+          <t>-1,25; 13,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,64; 16,82</t>
+          <t>2,85; 17,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,47; 3,8</t>
+          <t>-5,95; 6,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,81; 60,88</t>
+          <t>6,23; 64,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 29,51</t>
+          <t>-2,35; 29,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,76; 64,19</t>
+          <t>9,4; 65,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-52,42; 28,69</t>
+          <t>-28,16; 48,0</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,38</t>
+          <t>0,64</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-12,82%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 16,48</t>
+          <t>-1,49; 15,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 18,51</t>
+          <t>-2,16; 18,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 13,59</t>
+          <t>-5,3; 13,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 3,56</t>
+          <t>-4,68; 5,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 85,32</t>
+          <t>-4,9; 82,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 44,59</t>
+          <t>-4,14; 42,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,55; 36,66</t>
+          <t>-10,56; 35,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-56,26; 41,19</t>
+          <t>-33,34; 62,14</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5,99</t>
+          <t>5,43</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>29,7%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,74; 1,96</t>
+          <t>-14,09; 1,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 14,63</t>
+          <t>-2,25; 15,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 12,82</t>
+          <t>-4,35; 11,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,21; 12,21</t>
+          <t>-0,78; 11,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-35,8; 7,1</t>
+          <t>-36,07; 5,96</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 35,79</t>
+          <t>-4,36; 37,93</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-11,99; 49,96</t>
+          <t>-13,33; 47,76</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,21; 79,81</t>
+          <t>-4,11; 70,31</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24,29</t>
+          <t>2,5</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>456,61%</t>
+          <t>43,68%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,03; 15,56</t>
+          <t>4,86; 16,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 10,02</t>
+          <t>-1,66; 9,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,67; 14,89</t>
+          <t>4,79; 15,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,19; 59,91</t>
+          <t>-0,07; 5,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,14; 60,08</t>
+          <t>14,87; 61,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 24,33</t>
+          <t>-3,42; 24,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,96; 62,67</t>
+          <t>16,61; 64,51</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>19,63; 1408,93</t>
+          <t>-2,24; 122,07</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14,49</t>
+          <t>8,42</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>36,61%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 6,76</t>
+          <t>-2,7; 6,7</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,07; 13,74</t>
+          <t>3,72; 14,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,62; 14,17</t>
+          <t>4,33; 14,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,82; 25,2</t>
+          <t>4,18; 12,82</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 25,86</t>
+          <t>-8,67; 24,86</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,14; 35,77</t>
+          <t>8,51; 36,92</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,25; 43,11</t>
+          <t>10,96; 42,6</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>29,66; 313,13</t>
+          <t>16,57; 63,46</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9,43</t>
+          <t>4,47</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>33,01%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,11; 7,68</t>
+          <t>3,04; 7,85</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,44; 9,13</t>
+          <t>4,29; 9,13</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,2; 9,97</t>
+          <t>5,07; 9,62</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,08; 24,31</t>
+          <t>2,87; 6,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>10,26; 27,4</t>
+          <t>10,01; 28,25</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,73; 21,1</t>
+          <t>9,28; 20,8</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,81; 32,61</t>
+          <t>15,87; 31,99</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>31,86; 234,0</t>
+          <t>19,5; 49,15</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2C_R2-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R2-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son no remunerados</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados y estos son no remunerados</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
